--- a/dae_il/감사조서/dae_il_mapping_list_25년.xlsx
+++ b/dae_il/감사조서/dae_il_mapping_list_25년.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\lbh00\OneDrive\문서\감사\감사자료\audit-automation\dae_il\감사조서\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD45702D-3D7C-4C00-AD0F-6C7E79E53F60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64DFE9A7-7A53-4BB2-9E88-091D7160F0CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{A5EA571E-217A-4572-95DC-A5A70747DCE3}"/>
   </bookViews>
@@ -517,7 +517,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -540,12 +540,6 @@
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
@@ -892,7 +886,14 @@
   <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="9" width="28.9140625" customWidth="1"/>
+    <col min="1" max="1" width="17.08203125" customWidth="1"/>
+    <col min="2" max="2" width="28.9140625" customWidth="1"/>
+    <col min="3" max="3" width="26.1640625" customWidth="1"/>
+    <col min="4" max="4" width="15.9140625" customWidth="1"/>
+    <col min="5" max="6" width="28.9140625" customWidth="1"/>
+    <col min="7" max="7" width="23.83203125" customWidth="1"/>
+    <col min="8" max="8" width="14.4140625" customWidth="1"/>
+    <col min="9" max="9" width="14.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -1048,29 +1049,29 @@
       <c r="I6" s="7"/>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="10"/>
+      <c r="D7" s="8"/>
       <c r="E7" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="G7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="H7" s="11">
+      <c r="H7" s="9">
         <v>100000000</v>
       </c>
-      <c r="I7" s="9" t="s">
+      <c r="I7" s="6" t="s">
         <v>37</v>
       </c>
     </row>

--- a/dae_il/감사조서/dae_il_mapping_list_25년.xlsx
+++ b/dae_il/감사조서/dae_il_mapping_list_25년.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\lbh00\OneDrive\문서\감사\감사자료\audit-automation\dae_il\감사조서\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64DFE9A7-7A53-4BB2-9E88-091D7160F0CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56D49913-C3AE-4229-9FB3-854994F3246B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{A5EA571E-217A-4572-95DC-A5A70747DCE3}"/>
+    <workbookView xWindow="-19298" yWindow="-98" windowWidth="19396" windowHeight="12196" xr2:uid="{A5EA571E-217A-4572-95DC-A5A70747DCE3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
